--- a/src_code/results/jxr_500kb_evaluation_metrics_summary_wavelet.xlsx
+++ b/src_code/results/jxr_500kb_evaluation_metrics_summary_wavelet.xlsx
@@ -525,55 +525,55 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
-      </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -610,28 +610,28 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2</v>
-      </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -641,55 +641,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" t="n">
         <v>8</v>
       </c>
-      <c r="D4" t="n">
-        <v>93</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="Q4" t="n">
         <v>8</v>
       </c>
-      <c r="H4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -699,55 +699,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>23</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -757,55 +757,55 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -815,55 +815,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
         <v>8</v>
       </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>7</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -873,55 +873,55 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -931,55 +931,55 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -992,52 +992,52 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,55 +1047,55 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1105,55 +1105,55 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L12" t="n">
-        <v>355</v>
+        <v>39</v>
       </c>
       <c r="M12" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="R12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -1163,25 +1163,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1193,25 +1193,25 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>20</v>
-      </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1221,55 +1221,55 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H14" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="M14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="N14" t="n">
-        <v>366</v>
+        <v>26</v>
       </c>
       <c r="O14" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="R14" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
@@ -1279,52 +1279,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7</v>
+      </c>
+      <c r="M15" t="n">
         <v>6</v>
       </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O15" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
         <v>3</v>
@@ -1337,55 +1337,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K16" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L16" t="n">
         <v>18</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="O16" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="P16" t="n">
-        <v>232</v>
+        <v>26</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -1395,55 +1395,55 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q17" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1453,55 +1453,55 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="n">
+      <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4</v>
-      </c>
       <c r="N18" t="n">
         <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.2392638036809816</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.2653061224489796</v>
       </c>
       <c r="D2" t="n">
-        <v>0.695364238410596</v>
+        <v>0.2516129032258064</v>
       </c>
       <c r="E2" t="n">
         <v>147</v>
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5142857142857142</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3185840707964602</v>
+        <v>0.08376963350785341</v>
       </c>
       <c r="E3" t="n">
         <v>35</v>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6158940397350994</v>
+        <v>0.09174311926605505</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5886075949367089</v>
+        <v>0.1265822784810127</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6019417475728155</v>
+        <v>0.1063829787234043</v>
       </c>
       <c r="E4" t="n">
         <v>158</v>
@@ -1604,13 +1604,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3650793650793651</v>
+        <v>0.01418439716312057</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.06896551724137931</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.02352941176470588</v>
       </c>
       <c r="E5" t="n">
         <v>29</v>
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.495049504950495</v>
+        <v>0.05442176870748299</v>
       </c>
       <c r="C6" t="n">
-        <v>0.78125</v>
+        <v>0.125</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.07582938388625593</v>
       </c>
       <c r="E6" t="n">
         <v>64</v>
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5407407407407407</v>
+        <v>0.06315789473684211</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6636363636363637</v>
+        <v>0.1090909090909091</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5959183673469388</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
         <v>110</v>
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2558139534883721</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5689655172413793</v>
+        <v>0.1379310344827586</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.0583941605839416</v>
       </c>
       <c r="E8" t="n">
         <v>58</v>
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.69375</v>
+        <v>0.02941176470588235</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9173553719008265</v>
+        <v>0.03305785123966942</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7900355871886121</v>
+        <v>0.0311284046692607</v>
       </c>
       <c r="E9" t="n">
         <v>121</v>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.0379746835443038</v>
       </c>
       <c r="C10" t="n">
-        <v>0.875</v>
+        <v>0.05</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.04316546762589928</v>
       </c>
       <c r="E10" t="n">
         <v>120</v>
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7005649717514124</v>
+        <v>0.05333333333333334</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6888888888888889</v>
+        <v>0.04444444444444445</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6946778711484594</v>
+        <v>0.04848484848484848</v>
       </c>
       <c r="E11" t="n">
         <v>180</v>
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8830845771144279</v>
+        <v>0.2746478873239437</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6787762906309751</v>
+        <v>0.0745697896749522</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7675675675675676</v>
+        <v>0.1172932330827068</v>
       </c>
       <c r="E12" t="n">
         <v>523</v>
@@ -1756,13 +1756,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3125</v>
+        <v>0.006944444444444444</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>0.425531914893617</v>
+        <v>0.01149425287356322</v>
       </c>
       <c r="E13" t="n">
         <v>30</v>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.915</v>
+        <v>0.1857142857142857</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7024952015355086</v>
+        <v>0.04990403071017274</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7947882736156352</v>
+        <v>0.07866868381240545</v>
       </c>
       <c r="E14" t="n">
         <v>521</v>
@@ -1794,13 +1794,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5405405405405406</v>
+        <v>0.03061224489795918</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.05714285714285714</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6324110671936759</v>
+        <v>0.03986710963455149</v>
       </c>
       <c r="E15" t="n">
         <v>105</v>
@@ -1813,13 +1813,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.928</v>
+        <v>0.1805555555555556</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.06403940886699508</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.09454545454545454</v>
       </c>
       <c r="E16" t="n">
         <v>406</v>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.03007518796992481</v>
       </c>
       <c r="C17" t="n">
-        <v>0.632183908045977</v>
+        <v>0.04597701149425287</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6010928961748634</v>
+        <v>0.03636363636363636</v>
       </c>
       <c r="E17" t="n">
         <v>87</v>
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1935483870967742</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2307692307692308</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>42</v>
@@ -1870,16 +1870,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6779970760233918</v>
+        <v>0.07931286549707603</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6779970760233918</v>
+        <v>0.07931286549707603</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6779970760233918</v>
+        <v>0.07931286549707603</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6779970760233918</v>
+        <v>0.07931286549707603</v>
       </c>
     </row>
     <row r="20">
@@ -1889,13 +1889,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5621785275962041</v>
+        <v>0.08119761525665903</v>
       </c>
       <c r="C20" t="n">
-        <v>0.670855782316365</v>
+        <v>0.08905388336606736</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5912849290378562</v>
+        <v>0.06944291545789963</v>
       </c>
       <c r="E20" t="n">
         <v>2736</v>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7483215794330618</v>
+        <v>0.1468970798622349</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6779970760233918</v>
+        <v>0.07931286549707603</v>
       </c>
       <c r="D21" t="n">
-        <v>0.694697519671332</v>
+        <v>0.08791455240929734</v>
       </c>
       <c r="E21" t="n">
         <v>2736</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6779970760233918</v>
+        <v>0.07931286549707603</v>
       </c>
     </row>
     <row r="3">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7483215794330618</v>
+        <v>0.1468970798622349</v>
       </c>
     </row>
     <row r="4">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6779970760233918</v>
+        <v>0.07931286549707603</v>
       </c>
     </row>
     <row r="5">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.694697519671332</v>
+        <v>0.08791455240929734</v>
       </c>
     </row>
   </sheetData>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8388241470799775</v>
+        <v>0.5025411297760423</v>
       </c>
     </row>
     <row r="3">
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6567982456140351</v>
+        <v>0.03691520467836257</v>
       </c>
     </row>
     <row r="4">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6776315789473685</v>
+        <v>0.07200292397660819</v>
       </c>
     </row>
     <row r="5">
